--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T05:20:25+00:00</t>
+    <t>2026-09-28T10:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:16:57+00:00</t>
+    <t>2026-09-28T10:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:26:56+00:00</t>
+    <t>2026-09-28T11:29:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:29:30+00:00</t>
+    <t>2026-09-28T12:11:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -733,14 +733,14 @@
     <t>EpisodeOfCare.diagnosis.condition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/onko-condition)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-diagnose-primaertumor)
 </t>
   </si>
   <si>
     <t>Diagnose</t>
   </si>
   <si>
-    <t>Referenz auf die adressierte Tumorerkrankung OnkoCondition.</t>
+    <t>Referenz auf die adressierte Tumorerkrankung nach MII-Onkologie-Diagnoseprofil.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1225,7 +1225,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="104.53515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:11:39+00:00</t>
+    <t>2026-09-28T20:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T20:57:11+00:00</t>
+    <t>2026-09-28T21:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-line.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T21:01:12+00:00</t>
+    <t>2026-09-30T11:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
